--- a/3D print files/Bill of Material quantum dice.xlsx
+++ b/3D print files/Bill of Material quantum dice.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aernoutvanrossum/Github/Quantum-Dice-by-UTwente/3D print files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AD8110-FC91-554F-BD39-36809DF21B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4847193-C6D0-6A41-BF3E-D2E616E83A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="860" windowWidth="28800" windowHeight="15800" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
   </bookViews>
@@ -2044,6 +2044,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF458063C0B8354687E7E385217DADDD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="db0b04aaa15c7297f6f6526469376690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5f810545-bb7d-498e-98a6-3cc8175571c8" xmlns:ns3="8077f6fe-c9e5-4688-b004-da2992bb8cd8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="66dfeb35f9f6b101ff511922eb62fa51" ns2:_="" ns3:_="">
     <xsd:import namespace="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
@@ -2250,15 +2259,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D196A880-6C6D-4D69-8998-929C3B39CF40}">
   <ds:schemaRefs>
@@ -2277,6 +2277,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2293,12 +2301,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/3D print files/Bill of Material quantum dice.xlsx
+++ b/3D print files/Bill of Material quantum dice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aernoutvanrossum/Github/Quantum-Dice-by-UTwente/3D print files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4847193-C6D0-6A41-BF3E-D2E616E83A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89666273-BD4A-7742-A44F-96FF981E8E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="860" windowWidth="28800" windowHeight="15800" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
   </bookViews>
@@ -165,7 +165,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Thickness: max 15 mm
+          <t xml:space="preserve">Thickness: max 18 mm
 </t>
         </r>
         <r>
@@ -185,7 +185,18 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Connector: JST plug (red) or JST-PH (2 pole), 2mm
+          <t xml:space="preserve">Connector: JST-PH (2 pole), 2mm
+Check Polarity. See attached image
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
         </r>
       </text>
@@ -200,16 +211,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">version 103048 or 121048.
+Check polarity! If not ok, request swap of polarity through message center
 </t>
         </r>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
           </rPr>
-          <t>These batteries have a JST-XH 2.54 mm connector. Request a JST-PH 2.0 connector via Message Center</t>
+          <t>JST2.0 connector</t>
         </r>
       </text>
     </comment>
@@ -266,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="87">
   <si>
     <t>1.28 inch IPS Color TFT LCD Display Module 1.28" RGB LED Round Touch Screen GC9A01 Drive 4 Wire SPI Interface 240x240 PCB Board</t>
   </si>
@@ -514,13 +527,19 @@
     <t>Allen cylinder head screw, M3x16</t>
   </si>
   <si>
-    <t>Lipo-batterij 3.7V, 1100mAh 20C1100mAh, model xx3048</t>
-  </si>
-  <si>
-    <t>https://www.aliexpress.us/item/3256809160966846.html?gatewayAdapt=glo2usa4itemAdapt</t>
-  </si>
-  <si>
     <t>see tab "TPUFrameOnly"</t>
+  </si>
+  <si>
+    <t>Lipo-batterij 3.7V, 1800mAh 20C1800mAh, model xx3048</t>
+  </si>
+  <si>
+    <t>USB-A to USB-C charger cable</t>
+  </si>
+  <si>
+    <t>https://www.conrad.nl/nl/p/renkforce-rf-4288947-usb-kabel-usb-2-0-usb-a-stekker-usb-c-stekker-1-00-m-zwart-vergulde-steekcontacten-1429649.html</t>
+  </si>
+  <si>
+    <t>https://aliexpress.com/item/1005009325914720.html</t>
   </si>
 </sst>
 </file>
@@ -530,7 +549,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;€&quot;\ * #,##0.00_);_(&quot;€&quot;\ * \(#,##0.00\);_(&quot;€&quot;\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -586,6 +605,13 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -636,6 +662,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Afbeelding 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13D4B18C-1165-98F6-EC36-B9DD2FA76B55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17983200" y="5003800"/>
+          <a:ext cx="3860800" cy="2895600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -955,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B6AF03-25E8-2042-B8EE-7BB1F35ABDC9}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -1049,7 +1124,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:C36" si="0">$C$2*D12+$C$3*E12</f>
+        <f t="shared" ref="C12:C37" si="0">$C$2*D12+$C$3*E12</f>
         <v>2</v>
       </c>
       <c r="D12" s="4">
@@ -1408,7 +1483,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
@@ -1421,44 +1496,44 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="E37" s="4"/>
+      <c r="B37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39">
-        <f t="shared" ref="C39:C44" si="1">$C$2*D39+$C$3*E39</f>
-        <v>2</v>
-      </c>
-      <c r="D39" s="4">
-        <v>1</v>
-      </c>
-      <c r="E39" s="4">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C40">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C40:C45" si="1">$C$2*D40+$C$3*E40</f>
         <v>2</v>
       </c>
       <c r="D40" s="4">
@@ -1468,12 +1543,12 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
@@ -1486,12 +1561,12 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
@@ -1504,56 +1579,66 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D43" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D44" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B46" s="2" t="s">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B47" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B47" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1561,79 +1646,87 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B51" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+    <row r="52" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
         <v>67</v>
       </c>
-      <c r="C51">
-        <f t="shared" ref="C51:C54" si="2">$C$2*D51+$C$3*E51</f>
+      <c r="C52">
+        <f t="shared" ref="C52:C55" si="2">$C$2*D52+$C$3*E52</f>
         <v>55</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D52" s="4">
         <f>55/2</f>
         <v>27.5</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E52" s="4">
         <f>55/2</f>
         <v>27.5</v>
       </c>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="52" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
+      <c r="F52" s="8"/>
+    </row>
+    <row r="53" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
         <v>68</v>
       </c>
-      <c r="C52">
+      <c r="C53">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D53" s="4">
         <f>58/2</f>
         <v>29</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E53" s="4">
         <f>58/2</f>
         <v>29</v>
       </c>
-      <c r="F52" s="8"/>
-    </row>
-    <row r="53" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
+      <c r="F53" s="8"/>
+    </row>
+    <row r="54" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
         <v>69</v>
       </c>
-      <c r="C53">
+      <c r="C54">
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D54" s="4">
         <v>33</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E54" s="4">
         <v>33</v>
       </c>
-      <c r="F53" s="8"/>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
+      <c r="F54" s="8"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
         <v>70</v>
       </c>
-      <c r="C54">
+      <c r="C55">
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D55" s="4">
         <f>126/2</f>
         <v>63</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E55" s="4">
         <f>126/2</f>
         <v>63</v>
       </c>
@@ -1645,17 +1738,17 @@
     <hyperlink ref="F27" r:id="rId3" xr:uid="{A0714A2B-EF63-F240-A921-36F4B00EF898}"/>
     <hyperlink ref="F33" r:id="rId4" xr:uid="{78E5F7DE-88B7-1D44-AC85-653F1AB3B631}"/>
     <hyperlink ref="F34" r:id="rId5" xr:uid="{7FB9A456-9508-2845-A4B6-4DEC9C4B657D}"/>
-    <hyperlink ref="F44" r:id="rId6" xr:uid="{29DE5F51-B5E9-6546-B0ED-D93821AF97AE}"/>
-    <hyperlink ref="F43" r:id="rId7" xr:uid="{45C3A175-09CF-3C4E-8B60-4576540511C0}"/>
-    <hyperlink ref="F42" r:id="rId8" xr:uid="{BC2E6EAB-F4C8-334D-AC1D-D3F5417E6ACE}"/>
-    <hyperlink ref="F39" r:id="rId9" xr:uid="{4CA5F8F4-9815-8942-B98E-8375FCA3C7B2}"/>
-    <hyperlink ref="F40" r:id="rId10" xr:uid="{9DC6EDF5-311E-084A-AD02-E0859B9D1D78}"/>
+    <hyperlink ref="F45" r:id="rId6" xr:uid="{29DE5F51-B5E9-6546-B0ED-D93821AF97AE}"/>
+    <hyperlink ref="F44" r:id="rId7" xr:uid="{45C3A175-09CF-3C4E-8B60-4576540511C0}"/>
+    <hyperlink ref="F43" r:id="rId8" xr:uid="{BC2E6EAB-F4C8-334D-AC1D-D3F5417E6ACE}"/>
+    <hyperlink ref="F40" r:id="rId9" xr:uid="{4CA5F8F4-9815-8942-B98E-8375FCA3C7B2}"/>
+    <hyperlink ref="F41" r:id="rId10" xr:uid="{9DC6EDF5-311E-084A-AD02-E0859B9D1D78}"/>
     <hyperlink ref="F35" r:id="rId11" xr:uid="{4D119E3A-09A7-884C-B9FF-09D40E8F4386}"/>
     <hyperlink ref="F11" r:id="rId12" xr:uid="{69EE7F58-86AB-5C42-9D90-993C46E8D321}"/>
     <hyperlink ref="F12:F22" r:id="rId13" display="https://github.com/qlab-utwente/Quantum-Dice-by-UTwente/tree/main/3D%20print%20files/quantum%20dice%203D%20print%20parts%20TPUFrameOnly" xr:uid="{F1AB62F5-AC28-0A43-9BB4-0725CAEB4FF4}"/>
-    <hyperlink ref="F36" r:id="rId14" xr:uid="{4C8607C2-3BA6-B04D-976B-810B664A7063}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId14"/>
   <legacyDrawing r:id="rId15"/>
 </worksheet>
 </file>
@@ -1931,7 +2024,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
@@ -1942,7 +2035,7 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
@@ -1953,7 +2046,7 @@
         <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
@@ -1961,7 +2054,7 @@
         <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
@@ -2033,26 +2126,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF458063C0B8354687E7E385217DADDD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="db0b04aaa15c7297f6f6526469376690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5f810545-bb7d-498e-98a6-3cc8175571c8" xmlns:ns3="8077f6fe-c9e5-4688-b004-da2992bb8cd8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="66dfeb35f9f6b101ff511922eb62fa51" ns2:_="" ns3:_="">
     <xsd:import namespace="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
@@ -2259,32 +2332,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D196A880-6C6D-4D69-8998-929C3B39CF40}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
-    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2301,4 +2369,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D196A880-6C6D-4D69-8998-929C3B39CF40}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
+    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/3D print files/Bill of Material quantum dice.xlsx
+++ b/3D print files/Bill of Material quantum dice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aernoutvanrossum/Github/Quantum-Dice-by-UTwente/3D print files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B54780-2D97-794A-A460-48CF00EBFCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BF6230-20F6-7346-8DC7-C49DA6BB5A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="36540" windowHeight="18120" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15960" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
   </bookViews>
   <sheets>
     <sheet name="TPUFrameOnly" sheetId="2" r:id="rId1"/>
@@ -1452,14 +1452,35 @@
     <hyperlink ref="E32" r:id="rId11" xr:uid="{4D119E3A-09A7-884C-B9FF-09D40E8F4386}"/>
     <hyperlink ref="E10" r:id="rId12" xr:uid="{69EE7F58-86AB-5C42-9D90-993C46E8D321}"/>
     <hyperlink ref="E11:E19" r:id="rId13" display="https://github.com/qlab-utwente/Quantum-Dice-by-UTwente/tree/main/3D%20print%20files/quantum%20dice%203D%20print%20parts%20TPUFrameOnly" xr:uid="{F1AB62F5-AC28-0A43-9BB4-0725CAEB4FF4}"/>
+    <hyperlink ref="E29" r:id="rId14" xr:uid="{3F271A1C-56E6-A041-9730-1CA5C8FB6613}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId14"/>
-  <legacyDrawing r:id="rId15"/>
+  <drawing r:id="rId15"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF458063C0B8354687E7E385217DADDD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="db0b04aaa15c7297f6f6526469376690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5f810545-bb7d-498e-98a6-3cc8175571c8" xmlns:ns3="8077f6fe-c9e5-4688-b004-da2992bb8cd8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="66dfeb35f9f6b101ff511922eb62fa51" ns2:_="" ns3:_="">
     <xsd:import namespace="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
@@ -1666,41 +1687,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
-    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1723,9 +1713,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
+    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/3D print files/Bill of Material quantum dice.xlsx
+++ b/3D print files/Bill of Material quantum dice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aernoutvanrossum/Github/Quantum-Dice-by-UTwente/3D print files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BF6230-20F6-7346-8DC7-C49DA6BB5A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E715D3F6-8578-6945-BF91-A5B29485E03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15960" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
+    <workbookView xWindow="11200" yWindow="600" windowWidth="28800" windowHeight="15960" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
   </bookViews>
   <sheets>
     <sheet name="TPUFrameOnly" sheetId="2" r:id="rId1"/>
@@ -200,7 +200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
   <si>
     <t>1.28 inch IPS Color TFT LCD Display Module 1.28" RGB LED Round Touch Screen GC9A01 Drive 4 Wire SPI Interface 240x240 PCB Board</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>02D_Blue_PLA_V*_display_cup_top_bottom</t>
+  </si>
+  <si>
+    <t>https://nl.aliexpress.com/item/1005004379893877.html</t>
   </si>
 </sst>
 </file>
@@ -1357,6 +1360,11 @@
         <v>5</v>
       </c>
     </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E43" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>47</v>
@@ -1453,34 +1461,15 @@
     <hyperlink ref="E10" r:id="rId12" xr:uid="{69EE7F58-86AB-5C42-9D90-993C46E8D321}"/>
     <hyperlink ref="E11:E19" r:id="rId13" display="https://github.com/qlab-utwente/Quantum-Dice-by-UTwente/tree/main/3D%20print%20files/quantum%20dice%203D%20print%20parts%20TPUFrameOnly" xr:uid="{F1AB62F5-AC28-0A43-9BB4-0725CAEB4FF4}"/>
     <hyperlink ref="E29" r:id="rId14" xr:uid="{3F271A1C-56E6-A041-9730-1CA5C8FB6613}"/>
+    <hyperlink ref="E43" r:id="rId15" xr:uid="{B9C93A19-0F01-0F48-A6FD-83ED74C661E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId15"/>
-  <legacyDrawing r:id="rId16"/>
+  <drawing r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF458063C0B8354687E7E385217DADDD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="db0b04aaa15c7297f6f6526469376690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5f810545-bb7d-498e-98a6-3cc8175571c8" xmlns:ns3="8077f6fe-c9e5-4688-b004-da2992bb8cd8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="66dfeb35f9f6b101ff511922eb62fa51" ns2:_="" ns3:_="">
     <xsd:import namespace="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
@@ -1687,10 +1676,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
+    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1713,20 +1733,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
-    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/3D print files/Bill of Material quantum dice.xlsx
+++ b/3D print files/Bill of Material quantum dice.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aernoutvanrossum/Github/Quantum-Dice-by-UTwente/3D print files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E715D3F6-8578-6945-BF91-A5B29485E03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4CD169-3843-CD4A-9187-178D13D37E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11200" yWindow="600" windowWidth="28800" windowHeight="15960" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
+    <workbookView xWindow="11200" yWindow="600" windowWidth="34240" windowHeight="21140" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
   </bookViews>
   <sheets>
-    <sheet name="TPUFrameOnly" sheetId="2" r:id="rId1"/>
+    <sheet name="version2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -181,7 +181,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Check polarity! If not ok, request swap of polarity through message center
+          <t xml:space="preserve">Check polarity! If not ok, request swap of polarity through message center of Aliexpress
 </t>
         </r>
         <r>
@@ -200,7 +200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
   <si>
     <t>1.28 inch IPS Color TFT LCD Display Module 1.28" RGB LED Round Touch Screen GC9A01 Drive 4 Wire SPI Interface 240x240 PCB Board</t>
   </si>
@@ -334,9 +334,6 @@
     <t>02A_Yellow_TPU_V*_display_cup_power_USB-C</t>
   </si>
   <si>
-    <t>Frame parts of TPU, with bumper. Cups of PLA</t>
-  </si>
-  <si>
     <t>cable set, containing:</t>
   </si>
   <si>
@@ -398,6 +395,12 @@
   </si>
   <si>
     <t>https://nl.aliexpress.com/item/1005004379893877.html</t>
+  </si>
+  <si>
+    <t>Frame parts of TPU, with bumper. Cups of PLA. Software version &gt; V.2.0.0</t>
+  </si>
+  <si>
+    <t>For version 1.x.x the Blue top cup has an A and B indication</t>
   </si>
 </sst>
 </file>
@@ -903,7 +906,7 @@
         <v>31</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="2" t="s">
@@ -912,13 +915,18 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -934,7 +942,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -952,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -967,7 +975,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -982,7 +990,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -997,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1012,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1027,12 +1035,12 @@
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -1042,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
@@ -1057,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
@@ -1072,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
@@ -1087,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
@@ -1154,7 +1162,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26">
         <f t="shared" si="1"/>
@@ -1164,7 +1172,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
@@ -1219,7 +1227,7 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32">
         <f t="shared" si="2"/>
@@ -1234,7 +1242,7 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <f t="shared" si="2"/>
@@ -1244,12 +1252,12 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <f t="shared" si="2"/>
@@ -1259,15 +1267,15 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
@@ -1362,12 +1370,12 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
       <c r="E43" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1388,12 +1396,12 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49">
         <f t="shared" ref="C49:C52" si="4">$C$2*D49</f>
@@ -1407,7 +1415,7 @@
     </row>
     <row r="50" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50">
         <f t="shared" si="4"/>
@@ -1421,7 +1429,7 @@
     </row>
     <row r="51" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51">
         <f t="shared" si="4"/>
@@ -1434,7 +1442,7 @@
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52">
         <f t="shared" si="4"/>
@@ -1462,14 +1470,35 @@
     <hyperlink ref="E11:E19" r:id="rId13" display="https://github.com/qlab-utwente/Quantum-Dice-by-UTwente/tree/main/3D%20print%20files/quantum%20dice%203D%20print%20parts%20TPUFrameOnly" xr:uid="{F1AB62F5-AC28-0A43-9BB4-0725CAEB4FF4}"/>
     <hyperlink ref="E29" r:id="rId14" xr:uid="{3F271A1C-56E6-A041-9730-1CA5C8FB6613}"/>
     <hyperlink ref="E43" r:id="rId15" xr:uid="{B9C93A19-0F01-0F48-A6FD-83ED74C661E6}"/>
+    <hyperlink ref="E33" r:id="rId16" xr:uid="{E26307DB-87D9-CF49-ACEC-9FF4E814A6D9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
+  <drawing r:id="rId17"/>
+  <legacyDrawing r:id="rId18"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF458063C0B8354687E7E385217DADDD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="db0b04aaa15c7297f6f6526469376690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5f810545-bb7d-498e-98a6-3cc8175571c8" xmlns:ns3="8077f6fe-c9e5-4688-b004-da2992bb8cd8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="66dfeb35f9f6b101ff511922eb62fa51" ns2:_="" ns3:_="">
     <xsd:import namespace="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
@@ -1676,41 +1705,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
-    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1733,9 +1731,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
+    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/3D print files/Bill of Material quantum dice.xlsx
+++ b/3D print files/Bill of Material quantum dice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aernoutvanrossum/Github/Quantum-Dice-by-UTwente/3D print files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4CD169-3843-CD4A-9187-178D13D37E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D240F69-167D-0549-97BB-208FC9CADE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11200" yWindow="600" windowWidth="34240" windowHeight="21140" xr2:uid="{281531AD-289F-7444-9810-C417D6306E6A}"/>
   </bookViews>
@@ -358,9 +358,6 @@
     <t>TPU</t>
   </si>
   <si>
-    <t>https://github.com/qlab-utwente/Quantum-Dice-by-UTwente/tree/main/3D%20print%20files/quantum%20dice%203D%20print%20parts%20TPUFrameOnly</t>
-  </si>
-  <si>
     <t>Estimated 3D print material masses (gram)</t>
   </si>
   <si>
@@ -401,6 +398,9 @@
   </si>
   <si>
     <t>For version 1.x.x the Blue top cup has an A and B indication</t>
+  </si>
+  <si>
+    <t>https://github.com/qlab-utwente/Quantum-Dice-by-UTwente/tree/main/3D%20print%20files/Version%202</t>
   </si>
 </sst>
 </file>
@@ -410,7 +410,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;€&quot;\ * #,##0.00_);_(&quot;€&quot;\ * \(#,##0.00\);_(&quot;€&quot;\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -471,6 +471,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -906,7 +912,7 @@
         <v>31</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="2" t="s">
@@ -915,18 +921,18 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -942,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -960,7 +966,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -975,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -990,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1005,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1020,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1035,12 +1041,12 @@
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -1050,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
@@ -1065,7 +1071,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
@@ -1080,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
@@ -1095,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
@@ -1162,7 +1168,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26">
         <f t="shared" si="1"/>
@@ -1172,7 +1178,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
@@ -1242,7 +1248,7 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <f t="shared" si="2"/>
@@ -1252,12 +1258,12 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <f t="shared" si="2"/>
@@ -1267,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
@@ -1370,7 +1376,7 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
       <c r="E43" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
@@ -1396,7 +1402,7 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="17" x14ac:dyDescent="0.2">
@@ -1454,6 +1460,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E22" r:id="rId1" xr:uid="{13FB122D-0FED-1349-90B9-221BC590DC5C}"/>
     <hyperlink ref="E23" r:id="rId2" xr:uid="{EF523FE1-0C63-A944-AF6E-31D6D89950CF}"/>
@@ -1466,39 +1473,17 @@
     <hyperlink ref="E37" r:id="rId9" xr:uid="{4CA5F8F4-9815-8942-B98E-8375FCA3C7B2}"/>
     <hyperlink ref="E38" r:id="rId10" xr:uid="{9DC6EDF5-311E-084A-AD02-E0859B9D1D78}"/>
     <hyperlink ref="E32" r:id="rId11" xr:uid="{4D119E3A-09A7-884C-B9FF-09D40E8F4386}"/>
-    <hyperlink ref="E10" r:id="rId12" xr:uid="{69EE7F58-86AB-5C42-9D90-993C46E8D321}"/>
-    <hyperlink ref="E11:E19" r:id="rId13" display="https://github.com/qlab-utwente/Quantum-Dice-by-UTwente/tree/main/3D%20print%20files/quantum%20dice%203D%20print%20parts%20TPUFrameOnly" xr:uid="{F1AB62F5-AC28-0A43-9BB4-0725CAEB4FF4}"/>
-    <hyperlink ref="E29" r:id="rId14" xr:uid="{3F271A1C-56E6-A041-9730-1CA5C8FB6613}"/>
-    <hyperlink ref="E43" r:id="rId15" xr:uid="{B9C93A19-0F01-0F48-A6FD-83ED74C661E6}"/>
-    <hyperlink ref="E33" r:id="rId16" xr:uid="{E26307DB-87D9-CF49-ACEC-9FF4E814A6D9}"/>
+    <hyperlink ref="E29" r:id="rId12" xr:uid="{3F271A1C-56E6-A041-9730-1CA5C8FB6613}"/>
+    <hyperlink ref="E43" r:id="rId13" xr:uid="{B9C93A19-0F01-0F48-A6FD-83ED74C661E6}"/>
+    <hyperlink ref="E33" r:id="rId14" xr:uid="{E26307DB-87D9-CF49-ACEC-9FF4E814A6D9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId17"/>
-  <legacyDrawing r:id="rId18"/>
+  <drawing r:id="rId15"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF458063C0B8354687E7E385217DADDD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="db0b04aaa15c7297f6f6526469376690">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5f810545-bb7d-498e-98a6-3cc8175571c8" xmlns:ns3="8077f6fe-c9e5-4688-b004-da2992bb8cd8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="66dfeb35f9f6b101ff511922eb62fa51" ns2:_="" ns3:_="">
     <xsd:import namespace="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
@@ -1705,10 +1690,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5f810545-bb7d-498e-98a6-3cc8175571c8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8077f6fe-c9e5-4688-b004-da2992bb8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
+    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1731,20 +1747,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC96DF67-5917-4890-8162-737ED9540272}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA44028-4133-420E-8665-60C989F4E89B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5f810545-bb7d-498e-98a6-3cc8175571c8"/>
-    <ds:schemaRef ds:uri="8077f6fe-c9e5-4688-b004-da2992bb8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>